--- a/AAII_Financials/Yearly/AMT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>AMT</t>
   </si>
@@ -4469,26 +4469,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
+      <c r="D91" s="3">
+        <v>-1680400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1590000</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-1798100</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-1873600</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-1376700</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-1031700</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-991300</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>8</v>
